--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
@@ -215,7 +215,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b0cbeaf0-a586-4b2c-b87f-d2f79a7f6db0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{078a0c46-a171-4aea-93db-c02fced7bd99}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -300,7 +300,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3932ace5-e3c8-4049-9acc-166d4ea4d73d}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b35f17b3-86ab-4cad-a7a5-788e1fca4615}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -385,7 +385,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6cd9d0c2-31ce-4cc8-b1a3-7303931fe05e}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70a9e2d0-41ab-4696-8e94-b90e9ed6b4ed}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
@@ -215,7 +215,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{078a0c46-a171-4aea-93db-c02fced7bd99}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07682c01-ca09-4276-8945-d03f861f6da4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -300,7 +300,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b35f17b3-86ab-4cad-a7a5-788e1fca4615}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25a03ad1-0d93-46aa-9c6a-1ffd0d05d21a}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -385,7 +385,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70a9e2d0-41ab-4696-8e94-b90e9ed6b4ed}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7eba6342-9f5f-42fa-bbcf-c0266c812f00}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Common List_report.xlsx
@@ -215,7 +215,7 @@
         <xdr:cNvPr id="3" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07682c01-ca09-4276-8945-d03f861f6da4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1aecd7da-caad-45b5-b8b3-5fe7a50f8998}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -300,7 +300,7 @@
         <xdr:cNvPr id="4" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25a03ad1-0d93-46aa-9c6a-1ffd0d05d21a}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e964bfcc-b9be-4ebd-8341-8bb8c03a4a44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -385,7 +385,7 @@
         <xdr:cNvPr id="5" name="Text Box 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7eba6342-9f5f-42fa-bbcf-c0266c812f00}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5aaef538-2630-4211-ba97-623b839f1cd3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
